--- a/EKG_Kalite_Yönetim_Sistemi/98_Uygulama_Kayıtları/04_Parça ve Proses Kontrolü/EKG-KLT-PLN-08_yillik_kalibrasyon_plani__2024.xlsx
+++ b/EKG_Kalite_Yönetim_Sistemi/98_Uygulama_Kayıtları/04_Parça ve Proses Kontrolü/EKG-KLT-PLN-08_yillik_kalibrasyon_plani__2024.xlsx
@@ -1164,7 +1164,8 @@
   <pageSetup scale="80" orientation="landscape" verticalDpi="300" r:id="rId1"/>
   <headerFooter differentOddEven="0" differentFirst="0" scaleWithDoc="0" alignWithMargins="1">
     <oddHeader>&amp;L&amp;"Arial,Bold"&amp;11EKG-KLT-PLN-08&amp;C&amp;"Arial,Regular"&amp;11Yıllık Kalibrasyon Planı - 2024</oddHeader>
-    <oddFooter>&amp;L&amp;"Arial,Regular"&amp;11İlk Yayın: 04.05.2026 | Revizyon: 19.10.2026&amp;R&amp;11Sayfa &amp;P / &amp;N</oddFooter>
+    <oddFooter>&amp;L&amp;"Arial,Regular"&amp;11İlk Yayın: 05.06.2026 | Revizyon: 11.09.2026
+Revizyon nedeni: 2024 boş kaynak planı olarak adlandırıldı; cihaz/sertifika kanıtı bulunmadığı açıklandı.&amp;R&amp;11Sayfa &amp;P / &amp;N</oddFooter>
   </headerFooter>
   <drawing r:id="rId2"/>
 </worksheet>
